--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487139_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487139_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5335</v>
+        <v>1.9714</v>
       </c>
       <c r="E2" t="n">
-        <v>1.818</v>
+        <v>1.3361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7156</v>
+        <v>0.6353</v>
       </c>
       <c r="G2" t="n">
         <v>0.339</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0292</v>
+        <v>0.467</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7086</v>
+        <v>0.2268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3205</v>
+        <v>0.2402</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5717</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9758</v>
+        <v>1.5812</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9302</v>
+        <v>2.5891</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9544</v>
+        <v>-1.008</v>
       </c>
       <c r="G3" t="n">
         <v>1.1615</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6755</v>
+        <v>0.2809</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4574</v>
+        <v>0.1164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2181</v>
+        <v>0.1646</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5983</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.4306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4378</v>
+        <v>-0.0034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2734</v>
+        <v>0.434</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0478</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2102</v>
+        <v>-0.0704</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5619</v>
+        <v>0.1207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3517</v>
+        <v>-0.191</v>
       </c>
       <c r="V4" t="n">
         <v>1.5138</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0597</v>
+        <v>0.3055</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5243</v>
+        <v>-0.3052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.584</v>
+        <v>0.6107</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4571</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3431</v>
+        <v>0.589</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.078</v>
+        <v>0.1412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.421</v>
+        <v>0.4478</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9843</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0363</v>
+        <v>-0.1114</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5199</v>
+        <v>0.4792</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4836</v>
+        <v>-0.5906</v>
       </c>
       <c r="G6" t="n">
         <v>1.1139</v>
@@ -922,13 +922,13 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2855</v>
+        <v>0.1378</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0132</v>
+        <v>-0.0274</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2723</v>
+        <v>0.1652</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5561</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1679</v>
+        <v>-0.1152</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0388</v>
+        <v>1.2543</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1291</v>
+        <v>-1.3695</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1408</v>
+        <v>2.6678</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1262</v>
+        <v>1.6746</v>
       </c>
       <c r="I7" t="n">
-        <v>0.267</v>
+        <v>0.9932</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0207</v>
+        <v>3.6818</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0207</v>
+        <v>1.7283</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.9536</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1201</v>
+        <v>-1.0141</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1469</v>
+        <v>-0.0537</v>
       </c>
       <c r="O7" t="n">
-        <v>0.267</v>
+        <v>-0.9604</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3087</v>
+        <v>0.3751</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0595</v>
+        <v>0.0466</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2492</v>
+        <v>0.3285</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6385</v>
+        <v>-0.1411</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.965</v>
+        <v>-0.0388</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3265</v>
+        <v>-0.1023</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1335</v>
+        <v>0.1408</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.1262</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1335</v>
+        <v>0.267</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1335</v>
+        <v>0.1201</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.1469</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>0.267</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.772</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.2819</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0595</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.6385</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4938</v>
+        <v>-0.965</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3159</v>
+        <v>0.3265</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6678</v>
+        <v>0.1335</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6746</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9932</v>
+        <v>0.1335</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6818</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7283</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9536</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0141</v>
+        <v>0.1335</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0537</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9604</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9301</v>
+        <v>-0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0881</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3318</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7139</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1234</v>
+        <v>-4.0825</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1371</v>
+        <v>-4.1877</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0138</v>
+        <v>0.1052</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6178</v>
+        <v>-1.3316</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5463</v>
+        <v>2.4798</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.1641</v>
+        <v>-3.8114</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9956</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8472</v>
+        <v>2.4268</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.8428</v>
+        <v>-1.8971</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6222</v>
+        <v>-1.8613</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3009</v>
+        <v>0.053</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3213</v>
+        <v>-1.9143</v>
       </c>
       <c r="P10" t="n">
-        <v>0.772</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1231</v>
+        <v>-5.0182</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8951</v>
+        <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2941</v>
+        <v>0.1213</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0185</v>
+        <v>0.0149</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3126</v>
+        <v>0.1064</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5717</v>
+        <v>-0.9421</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2177</v>
+        <v>-4.2582</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9482</v>
+        <v>-3.9775</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2695</v>
+        <v>-0.2807</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3316</v>
+        <v>-4.6178</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4798</v>
+        <v>1.5463</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8114</v>
+        <v>-6.1641</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5296999999999999</v>
+        <v>-1.9956</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4268</v>
+        <v>1.8472</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8971</v>
+        <v>-3.8428</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8613</v>
+        <v>-2.6222</v>
       </c>
       <c r="N11" t="n">
-        <v>0.053</v>
+        <v>-0.3009</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9143</v>
+        <v>-2.3213</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.0182</v>
+        <v>-2.1231</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0881</v>
+        <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0139</v>
+        <v>0.1593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7456</v>
+        <v>0.1412</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2684</v>
+        <v>0.0181</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9421</v>
+        <v>-0.5717</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6531</v>
+        <v>-5.058199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4137</v>
+        <v>-3.8189</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2392</v>
+        <v>-1.2394</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8978000000000002</v>
@@ -1375,13 +1375,13 @@
         <v>-11.1755</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9042</v>
+        <v>-0.9041999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-10.2714</v>
       </c>
       <c r="P12" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.4055</v>
@@ -1390,13 +1390,13 @@
         <v>16.4055</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1832</v>
+        <v>1.7781</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1255999999999999</v>
+        <v>0.7209</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0572</v>
+        <v>1.0574</v>
       </c>
       <c r="V12" t="n">
         <v>-5.9384</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.889699999999999</v>
+        <v>6.5981</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8194</v>
+        <v>5.117</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0703</v>
+        <v>1.4811</v>
       </c>
       <c r="G13" t="n">
         <v>0.8339</v>
@@ -1468,13 +1468,13 @@
         <v>2.8951</v>
       </c>
       <c r="S13" t="n">
-        <v>3.098</v>
+        <v>0.8064</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1483</v>
+        <v>0.4459</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9498</v>
+        <v>0.3605</v>
       </c>
       <c r="V13" t="n">
         <v>3.0277</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.938</v>
+        <v>3.3579</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3958</v>
+        <v>2.6821</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5422</v>
+        <v>0.6758</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4202</v>
+        <v>3.8993</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0646</v>
+        <v>-0.6169</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6444</v>
+        <v>4.5162</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5729</v>
+        <v>4.3798</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.8424</v>
+        <v>0.6519</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2695</v>
+        <v>3.7279</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.4805</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2222</v>
+        <v>-1.2688</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3748</v>
+        <v>0.7883</v>
       </c>
       <c r="P14" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.3511</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.3161</v>
-      </c>
       <c r="S14" t="n">
-        <v>0.5512</v>
+        <v>0.0377</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5221</v>
+        <v>-0.0535</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0734</v>
+        <v>0.0912</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6236</v>
+        <v>2.8366</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0812</v>
+        <v>0.6963</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5423</v>
+        <v>2.1403</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8993</v>
+        <v>-1.4202</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6169</v>
+        <v>-3.0646</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5162</v>
+        <v>1.6444</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3798</v>
+        <v>-0.5729</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6519</v>
+        <v>-1.8424</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7279</v>
+        <v>1.2695</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4805</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2688</v>
+        <v>-1.2222</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7883</v>
+        <v>0.3748</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6967</v>
+        <v>0.4498</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6544</v>
+        <v>-0.2217</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0423</v>
+        <v>0.6715</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4981</v>
+        <v>2.1531</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9448</v>
+        <v>2.1451</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4467</v>
+        <v>0.0081</v>
       </c>
       <c r="G16" t="n">
         <v>2.2063</v>
@@ -1702,13 +1702,13 @@
         <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6623</v>
+        <v>-0.0073</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1057</v>
+        <v>0.0945</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5566</v>
+        <v>-0.1018</v>
       </c>
       <c r="V16" t="n">
         <v>1.8842</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.5319</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.047</v>
+        <v>-0.6478</v>
       </c>
       <c r="F17" t="n">
         <v>0.1159</v>
@@ -1780,10 +1780,10 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>0.505</v>
+        <v>-0.0959</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6214</v>
+        <v>0.0205</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1164</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6762</v>
+        <v>-0.5423</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5663</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8901</v>
+        <v>1.0239</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3621</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5493</v>
+        <v>-0.4154</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2518</v>
+        <v>-0.118</v>
       </c>
       <c r="V18" t="n">
         <v>0.6562</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6244</v>
+        <v>-1.3035</v>
       </c>
       <c r="E19" t="n">
         <v>-1.5844</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0401</v>
+        <v>0.2809</v>
       </c>
       <c r="G19" t="n">
         <v>-1.295</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3946</v>
+        <v>-0.0737</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2294</v>
+        <v>0.0915</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2466</v>
+        <v>-2.0661</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0183</v>
+        <v>-0.9182</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2282</v>
+        <v>-1.1479</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0492</v>
@@ -2014,13 +2014,13 @@
         <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1395</v>
+        <v>0.041</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0205</v>
+        <v>0.0598</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4344</v>
+        <v>-2.0804</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3621</v>
+        <v>-2.0616</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0723</v>
+        <v>-0.0188</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2396</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1369</v>
+        <v>-0.7829</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>-0.5324</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3041</v>
+        <v>-0.2505</v>
       </c>
       <c r="V21" t="n">
         <v>0.3281</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3836</v>
+        <v>-2.1007</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4239</v>
+        <v>-2.6228</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0403</v>
+        <v>0.5221</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1272</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7582</v>
+        <v>-0.4752</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1303</v>
+        <v>-0.3291</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.628</v>
+        <v>-0.1461</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8842</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.6532</v>
+        <v>6.320799999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>1.239199999999999</v>
+        <v>1.239399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4138</v>
+        <v>5.081400000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.898000000000001</v>
+        <v>0.8980000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-10.5156</v>
@@ -2248,16 +2248,16 @@
         <v>16.4058</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1833</v>
+        <v>-0.5155000000000001</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0572</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1258999999999998</v>
+        <v>0.5417</v>
       </c>
       <c r="V23" t="n">
-        <v>5.9383</v>
+        <v>5.938300000000001</v>
       </c>
       <c r="W23" t="n">
         <v>7.526999999999999</v>
